--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SPA</t>
+          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SpA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2167,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2362,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2488,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2614,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2679,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2744,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2874,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2939,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3004,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3069,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3134,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3199,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3520,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3585,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3650,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3715,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3841,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3906,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3971,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4036,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4101,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4166,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4231,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4296,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4361,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4617,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4682,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4747,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4812,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4877,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5003,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5129,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5194,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5259,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5324,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5389,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5454,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5519,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5584,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5649,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5775,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5840,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5905,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5970,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6035,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6100,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6165,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6230,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6295,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6360,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6425,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6490,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6555,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6620,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6685,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6750,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6815,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6880,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6945,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7010,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7075,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7140,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7205,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7270,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7396,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7461,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7526,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7591,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7656,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7721,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7786,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8095,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8160,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8225,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8290,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8355,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8420,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8485,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8611,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8676,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8741,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8867,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8932,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8997,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9062,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9127,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9192,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9257,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9322,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9387,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9574,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9639,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9704,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9769,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9834,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9899,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9964,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10151,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10216,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10281,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10346,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10411,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10476,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10541,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10606,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10671,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10736,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10801,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10866,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10992,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11057,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11183,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11309,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11435,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11500,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11565,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11630,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11695,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11760,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11886,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11951,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12016,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12142,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12207,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12272,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12398,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12463,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12528,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12593,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12780,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12906,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12971,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13097,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13162,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13227,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13292,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13357,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13422,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13548,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13613,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13678,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13743,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13808,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13873,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13938,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14003,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14068,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14133,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14198,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14263,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14328,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14393,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14458,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14523,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14588,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14653,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14718,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14905,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14970,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15035,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15100,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15165,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15230,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15295,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15360,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15425,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15490,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
